--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N89_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N89_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.23526755163668</v>
+        <v>10.60073097714096</v>
       </c>
       <c r="D2" t="n">
-        <v>65.04141023686064</v>
+        <v>10.56922916348985</v>
       </c>
       <c r="E2" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F2" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.04124833835877</v>
+        <v>11.3817028549833</v>
       </c>
       <c r="D3" t="n">
-        <v>70.06924255491484</v>
+        <v>11.38625191517366</v>
       </c>
       <c r="E3" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F3" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.86804315709907</v>
+        <v>4.5285570130286</v>
       </c>
       <c r="D4" t="n">
-        <v>26.49101366339832</v>
+        <v>4.304789720302226</v>
       </c>
       <c r="E4" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F4" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.04328747007198</v>
+        <v>3.094534213886697</v>
       </c>
       <c r="D5" t="n">
-        <v>17.9343399007614</v>
+        <v>2.914330233873727</v>
       </c>
       <c r="E5" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F5" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.12085910563908</v>
+        <v>4.732139604666352</v>
       </c>
       <c r="D6" t="n">
-        <v>29.89646107838323</v>
+        <v>4.858174925237274</v>
       </c>
       <c r="E6" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F6" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.77109007072029</v>
+        <v>8.087802136492048</v>
       </c>
       <c r="D7" t="n">
-        <v>50.58690713842438</v>
+        <v>8.220372409993962</v>
       </c>
       <c r="E7" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F7" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.92837360039518</v>
+        <v>10.06336071006422</v>
       </c>
       <c r="D8" t="n">
-        <v>74.34606622058742</v>
+        <v>12.08123576084546</v>
       </c>
       <c r="E8" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F8" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>72.51478927697048</v>
+        <v>11.7836532575077</v>
       </c>
       <c r="D9" t="n">
-        <v>6.191503108599854</v>
+        <v>1.006119255147476</v>
       </c>
       <c r="E9" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F9" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.60237055831637</v>
+        <v>6.110385215726411</v>
       </c>
       <c r="D10" t="n">
-        <v>57.85030530527803</v>
+        <v>9.400674612107681</v>
       </c>
       <c r="E10" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F10" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05536613099094</v>
+        <v>4.071496996286028</v>
       </c>
       <c r="D11" t="n">
-        <v>11.73249585306582</v>
+        <v>1.906530576123197</v>
       </c>
       <c r="E11" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F11" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.53002555655403</v>
+        <v>5.77362915294003</v>
       </c>
       <c r="D12" t="n">
-        <v>48.50460843672644</v>
+        <v>7.881998870968046</v>
       </c>
       <c r="E12" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F12" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.85468801899108</v>
+        <v>5.338886803086051</v>
       </c>
       <c r="D13" t="n">
-        <v>31.12493230089689</v>
+        <v>5.057801498895745</v>
       </c>
       <c r="E13" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F13" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>49.07160628798749</v>
+        <v>7.974136021797968</v>
       </c>
       <c r="D14" t="n">
-        <v>28.97911758833155</v>
+        <v>4.709106608103877</v>
       </c>
       <c r="E14" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F14" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.68690069709411</v>
+        <v>4.661621363277793</v>
       </c>
       <c r="D15" t="n">
-        <v>36.85092970813317</v>
+        <v>5.988276077571641</v>
       </c>
       <c r="E15" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F15" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>22.38354076495271</v>
+        <v>3.637325374304815</v>
       </c>
       <c r="D16" t="n">
-        <v>45.34367280352936</v>
+        <v>7.368346830573521</v>
       </c>
       <c r="E16" t="n">
-        <v>17.6082418426571</v>
+        <v>2.861339299431779</v>
       </c>
       <c r="F16" t="n">
-        <v>20.27494496447915</v>
+        <v>3.294678556727862</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
